--- a/output/pdf_financials_xlsx/TES.xlsx
+++ b/output/pdf_financials_xlsx/TES.xlsx
@@ -6707,49 +6707,49 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.55309</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.792672</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.874342</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.332142</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.508479</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.508479</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.508479</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.508479</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.697336</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.697336</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.697336</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.697336</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.697336</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.697336</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.697336</v>
       </c>
       <c r="S92" s="1" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>0.4578</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>3.50934</v>
+        <v>3.402594</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -10458,7 +10458,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -12378,7 +12382,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -15044,7 +15052,11 @@
           <t>Reserves (Note 6) 1,697,336</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -18018,7 +18030,11 @@
           <t>Reserves (Note 7) 1,697,336</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -23534,7 +23550,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -25710,7 +25730,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -27480,7 +27504,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -27984,7 +28012,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -35386,7 +35418,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TES.xlsx
+++ b/output/pdf_financials_xlsx/TES.xlsx
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00306</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008415000000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.009804</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.007213</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002734</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.251081</v>
+        <v>-0.254141</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.628031</v>
+        <v>-2.636446</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.143517</v>
+        <v>-1.153321</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.30117</v>
+        <v>-1.308383</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.07397</v>
+        <v>-3.076704</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.071429</v>
@@ -2546,19 +2546,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.251081</v>
+        <v>-0.254141</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.628031</v>
+        <v>-2.636446</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.143517</v>
+        <v>-1.153321</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.30117</v>
+        <v>-1.308383</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.07397</v>
+        <v>-3.076704</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.071429</v>
@@ -2916,40 +2916,40 @@
         <v>0.038473</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.039109</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.766606</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.390295</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.07023799999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.271694</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.109195</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.109195</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.19433</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.034521</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.11554</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.262443</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.028354</v>
       </c>
       <c r="S34" s="1" t="inlineStr">
         <is>
@@ -3042,40 +3042,40 @@
         <v>0.038473</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.039109</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.766606</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.390295</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.07023799999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.271694</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.109195</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.109195</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.19433</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.034521</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.11554</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.262443</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.028354</v>
       </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
@@ -3798,34 +3798,34 @@
         <v>0.030119</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.045228</v>
+        <v>0.006119</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.7754180000000001</v>
+        <v>0.008812</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.529791</v>
+        <v>0.139496</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.07911600000000001</v>
+        <v>0.008878</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.308705</v>
+        <v>0.037011</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.131735</v>
+        <v>0.02254</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.131735</v>
+        <v>0.02254</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.19926</v>
+        <v>0.00493</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.039111</v>
+        <v>0.00459</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.11979</v>
+        <v>0.00425</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -20360,7 +20360,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -51336,7 +51336,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -55942,7 +55942,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E443" s="5" t="n">

--- a/output/pdf_financials_xlsx/TES.xlsx
+++ b/output/pdf_financials_xlsx/TES.xlsx
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.043042</v>
+        <v>0.103542</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.096634</v>
+        <v>0.144634</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.136364</v>
+        <v>0.184364</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.233448</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.001255</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0.003516</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>28.840623</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>28.840623</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>30.948131</v>
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.13772</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.34422</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0.55309</v>
@@ -29476,7 +29476,11 @@
           <t>Equipment – Note 5</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -29578,7 +29582,11 @@
           <t>Mineral properties – Note 6</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -29892,7 +29900,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E194" s="5" t="n">
         <v>28.840623</v>
       </c>
@@ -30098,7 +30110,11 @@
           <t>Contributed surplus – Note 7</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E196" s="5" t="n">
         <v>0.13772</v>
       </c>
@@ -30622,7 +30638,11 @@
           <t>Prepaid expenses and deposit – Notes 4 and 13</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E201" s="5" t="n">
         <v>0.03</v>
       </c>
@@ -53456,7 +53476,11 @@
           <t>Management fees – Note 4</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E419" s="5" t="n">
         <v>0.022</v>
       </c>
@@ -56874,7 +56898,11 @@
           <t>Consulting fees and investor relations – Note 4</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E452" s="5" t="n">
         <v>0.0385</v>
       </c>
